--- a/output/cluster_vergleich/409480_Fischerwerke_GmbH___Co__KG_cluster.xlsx
+++ b/output/cluster_vergleich/409480_Fischerwerke_GmbH___Co__KG_cluster.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Fischerwerke GmbH &amp; Co. KG" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="NK_Konditionen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -593,4 +594,3035 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:V47"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Schlüssel</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Aktiv</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Aktive 
+Sendung 
+in Import- 
+/Export-
+Land</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Prüfung ERKA</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>wird geprüft 
+von</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>betrifft
+Abrechnung</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>betrifft
+Erfassung
+(manuell)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>betrifft
+EDI</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>betrifft
+Operative/
+Abfertigung</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Filler2</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>DFÜ 
+ja / Nein</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Bemerkungen AX-Team</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Umsatz 2024 P1-P9</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>PSS</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>PSS Umsatz 2024-2025</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Name, Straße, LKZ, PLZ Ort</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>Check Sendung 2024-2025</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>Column2
+SSS Satzart → Transportart:
+•1 – National
+•2 – Import
+•3 – Export
+•0 – Nicht 
+relevant</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>Land</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>Bemerkung / Hinweis für AX</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>Benutzergruppe
+•0 - Alle Benutzer     
+•5 - Abrechnung debitorisch 
+•6 - Abrechnung kreditorisch
+•1 / 2 / 3 / 4 / 8 – Nicht relevant</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Prüfungshinweis
+grün -&gt; in AX hinterlegt
+pink-&gt; in AX zu hinterlegen
+rot -&gt; in AX nicht relevant
+orange -&gt; in AX Routing prüfen/umsetzen
+blau -&gt; EDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>150522E</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>4 - betrifft Erfassung/ Abfertigung/ Operative</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>EDI</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>805925.4100000019</v>
+      </c>
+      <c r="N2" t="n">
+        <v>15052</v>
+      </c>
+      <c r="O2" t="n">
+        <v>15052</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>FISCHERWERKE GMBH &amp; CO. KG,  KLAUS-FISCHER-STR. 1,  D  72178  WALDACHTAL TUMLINGEN</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>150522E</t>
+        </is>
+      </c>
+      <c r="R2" t="n">
+        <v>2</v>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>KLEINSENDUNGEN BIS 50 KG AUS MONTROIG -&gt; BITTE | 0,1 STELLPLÄTZE ALS SPERRIGKEIT ERFASSEN | ************************************************** | 60 X 40 BIS MAX 100 KG = HALBPALETTE ERFASSEN | ************************************************** | ANSONSTEN ANZAHL DER STELLPLÄTZE ERFASSEN | (0,4 LM = 1 STELLPLATZ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>150522I</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>4 - betrifft Erfassung/ Abfertigung/ Operative</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>EDI</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>805925.4100000019</v>
+      </c>
+      <c r="N3" t="n">
+        <v>15052</v>
+      </c>
+      <c r="O3" t="n">
+        <v>15052</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>FISCHERWERKE GMBH &amp; CO. KG,  KLAUS-FISCHER-STR. 1,  D  72178  WALDACHTAL TUMLINGEN</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>150522I</t>
+        </is>
+      </c>
+      <c r="R3" t="n">
+        <v>2</v>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>***ZEITFENSTER FÜR IMPORTE AUS ITALIEN -&gt; IMMER*** | ***FIX DONNERSTAG UND MONTAG ZWISCHEN 7 + 8 UHR*** | --&gt; EX FISCHER PADOVA - VERSCH. ENTLADESTELLEN, |     PRO STOP EINEN AUFTRAG NACHERFASSEN. | --&gt; FZ- FISCHER PADOVA - FRANKATUR 89 + FZ 10576 | --&gt; FZ- FISCHER WALDA. - FRANKATUR 90 + FZ 15052 | --&gt; VD-SSP - BITTE NUR IN DER DFÜ-SDG. EX CESPED |     DAS GESAMTVOLUMEN EINTRAGEN, NACHDEM CESPED |     UNS BERECHNEN DARF (LM ODER CBM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>150523</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2 - wird benötigt in der Abrechnung - betrifft aber auch Erfassung</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Kobes</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>nicht meht benötigt (Leergut)</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>EDI</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>805925.4100000019</v>
+      </c>
+      <c r="N4" t="n">
+        <v>15052</v>
+      </c>
+      <c r="O4" t="n">
+        <v>15052</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>FISCHERWERKE GMBH &amp; CO. KG,  KLAUS-FISCHER-STR. 1,  D  72178  WALDACHTAL TUMLINGEN</t>
+        </is>
+      </c>
+      <c r="R4" t="n">
+        <v>3</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>betrifft EDI und Konditionierung</t>
+        </is>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>&gt; BITTE AUF FIRMIERUNG ACHTEN. | &gt; 43217 = FISCHER DEUTSCHLAND VERTRIEBS GMBH | &gt; FIS03 = FISCHERWERKE, HORB-ALTHEIM | &gt; 11999 = FISCHER AUTOMOTIVE HORB | &gt; EXP AT + BE &gt; IMMER "FP" ERFASSEN. | LIEFERSCHEINNUMMER  U N D  TRANSPORTNUMMER  !!!!ZWEITE LADESTELLE -&gt; BEHANDLUNGSHINWEIS 43 BITTE.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>150523B</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2 - wird benötigt in der Abrechnung - betrifft aber auch Erfassung</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>EDI</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>805925.4100000019</v>
+      </c>
+      <c r="N5" t="n">
+        <v>15052</v>
+      </c>
+      <c r="O5" t="n">
+        <v>15052</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>FISCHERWERKE GMBH &amp; CO. KG,  KLAUS-FISCHER-STR. 1,  D  72178  WALDACHTAL TUMLINGEN</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>150523B</t>
+        </is>
+      </c>
+      <c r="R5" t="n">
+        <v>3</v>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>doppelt</t>
+        </is>
+      </c>
+      <c r="U5" t="n">
+        <v>5</v>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>&gt; BITTE "FIS23" ERFASSEN !!!</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>150522</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>4 - betrifft Erfassung/ Abfertigung/ Operative</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>EDI</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>805925.4100000019</v>
+      </c>
+      <c r="N6" t="n">
+        <v>15052</v>
+      </c>
+      <c r="O6" t="n">
+        <v>15052</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>FISCHERWERKE GMBH &amp; CO. KG,  KLAUS-FISCHER-STR. 1,  D  72178  WALDACHTAL TUMLINGEN</t>
+        </is>
+      </c>
+      <c r="R6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>************************************************** | * ACHTUNG - FISCHER BEZAHLT NICHT MEHR OHNE POD  * | * WENN MIT DEM IMPORT-LKW DIREKT ZUGESTELLT WURDE* | * BITTE DEN POD SOFORT BEI AKTENKONTROLLE ANFOR- * | * DERN UND M I T DER AKTE ZUSAMMEN ZUR ABRECHNUNG* | * GEBEN.                                         * | **************************************************</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>150522</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>3 - wird benötigt in der Abrechnung</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>EDI</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>805925.4100000019</v>
+      </c>
+      <c r="N7" t="n">
+        <v>15052</v>
+      </c>
+      <c r="O7" t="n">
+        <v>15052</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>FISCHERWERKE GMBH &amp; CO. KG,  KLAUS-FISCHER-STR. 1,  D  72178  WALDACHTAL TUMLINGEN</t>
+        </is>
+      </c>
+      <c r="R7" t="n">
+        <v>2</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Prozess und Mail-Adresse noch aktuell?</t>
+        </is>
+      </c>
+      <c r="U7" t="n">
+        <v>5</v>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>ABLIEFERBELEGE PER MAIL MIT BEZUG AUF UNSERE | RG-NUMMER AN |       INGEBORG.TIPPELREITER@FISCHER.DE</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>150522I</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>3 - wird benötigt in der Abrechnung</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>EDI</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>805925.4100000019</v>
+      </c>
+      <c r="N8" t="n">
+        <v>15052</v>
+      </c>
+      <c r="O8" t="n">
+        <v>15052</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>FISCHERWERKE GMBH &amp; CO. KG,  KLAUS-FISCHER-STR. 1,  D  72178  WALDACHTAL TUMLINGEN</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>150522I</t>
+        </is>
+      </c>
+      <c r="R8" t="n">
+        <v>2</v>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>betrifft EDI</t>
+        </is>
+      </c>
+      <c r="U8" t="n">
+        <v>5</v>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>FZ PRÜFEN -&gt; MEIST FISCHER PADOVA 10576</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>150523A</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2 - wird benötigt in der Abrechnung - betrifft aber auch Erfassung</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Kobes</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>nicht meht benötigt (Leergut)</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>EDI</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>805925.4100000019</v>
+      </c>
+      <c r="N9" t="n">
+        <v>15052</v>
+      </c>
+      <c r="O9" t="n">
+        <v>15052</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>FISCHERWERKE GMBH &amp; CO. KG,  KLAUS-FISCHER-STR. 1,  D  72178  WALDACHTAL TUMLINGEN</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>150523A</t>
+        </is>
+      </c>
+      <c r="R9" t="n">
+        <v>3</v>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>betrifft EDI</t>
+        </is>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>&gt; BITTE IMMER "FP" ERFASSEN !</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>150523B</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2 - wird benötigt in der Abrechnung - betrifft aber auch Erfassung</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Kobes</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>nicht meht benötigt (Leergut)</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>EDI</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>805925.4100000019</v>
+      </c>
+      <c r="N10" t="n">
+        <v>15052</v>
+      </c>
+      <c r="O10" t="n">
+        <v>15052</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>FISCHERWERKE GMBH &amp; CO. KG,  KLAUS-FISCHER-STR. 1,  D  72178  WALDACHTAL TUMLINGEN</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>150523B</t>
+        </is>
+      </c>
+      <c r="R10" t="n">
+        <v>3</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>betrifft EDI</t>
+        </is>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>&gt; BITTE "FIS23" UND IMMER "FP" ERFASSEN !!!</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>150523CY</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>EDI</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
+        <v>805925.4100000019</v>
+      </c>
+      <c r="N11" t="n">
+        <v>15052</v>
+      </c>
+      <c r="O11" t="n">
+        <v>15052</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>FISCHERWERKE GMBH &amp; CO. KG,  KLAUS-FISCHER-STR. 1,  D  72178  WALDACHTAL TUMLINGEN</t>
+        </is>
+      </c>
+      <c r="R11" t="n">
+        <v>3</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>CY</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>keine aktive SDG in 2024</t>
+        </is>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>SDG. FÜR UNICOL NICOSIA SIND I.A. RHENUS - MUSS | VIA I 37 - IST GEROUTET</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>150523GR</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2 - wird benötigt in der Abrechnung - betrifft aber auch Erfassung</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>EDI</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>805925.4100000019</v>
+      </c>
+      <c r="N12" t="n">
+        <v>15052</v>
+      </c>
+      <c r="O12" t="n">
+        <v>15052</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>FISCHERWERKE GMBH &amp; CO. KG,  KLAUS-FISCHER-STR. 1,  D  72178  WALDACHTAL TUMLINGEN</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>150523GR</t>
+        </is>
+      </c>
+      <c r="R12" t="n">
+        <v>3</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>GR</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>betrifft EDI</t>
+        </is>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>&gt; SENDUNGEN EX DUS FÜR RAUM ATHEN = FIS20 |   UND STELLPLÄTZE ERFASSEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>150523GR</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2 - wird benötigt in der Abrechnung - betrifft aber auch Erfassung</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>EDI</t>
+        </is>
+      </c>
+      <c r="M13" t="n">
+        <v>805925.4100000019</v>
+      </c>
+      <c r="N13" t="n">
+        <v>15052</v>
+      </c>
+      <c r="O13" t="n">
+        <v>15052</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>FISCHERWERKE GMBH &amp; CO. KG,  KLAUS-FISCHER-STR. 1,  D  72178  WALDACHTAL TUMLINGEN</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>150523GR</t>
+        </is>
+      </c>
+      <c r="R13" t="n">
+        <v>3</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>GR</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>doppelt</t>
+        </is>
+      </c>
+      <c r="U13" t="n">
+        <v>5</v>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>&gt; SENDUNGEN EX DUS FÜR RAUM ATHEN = FIS20 |   UND STELLPLÄTZE ERFASSEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>150523I</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>4 - betrifft Erfassung/ Abfertigung/ Operative</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>EDI</t>
+        </is>
+      </c>
+      <c r="M14" t="n">
+        <v>805925.4100000019</v>
+      </c>
+      <c r="N14" t="n">
+        <v>15052</v>
+      </c>
+      <c r="O14" t="n">
+        <v>15052</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>FISCHERWERKE GMBH &amp; CO. KG,  KLAUS-FISCHER-STR. 1,  D  72178  WALDACHTAL TUMLINGEN</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>150523I</t>
+        </is>
+      </c>
+      <c r="R14" t="n">
+        <v>3</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>&gt; BEI FISCHER PADOVA, K E I N PALETTENTAUSCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>150523P</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>EDI</t>
+        </is>
+      </c>
+      <c r="M15" t="n">
+        <v>805925.4100000019</v>
+      </c>
+      <c r="N15" t="n">
+        <v>15052</v>
+      </c>
+      <c r="O15" t="n">
+        <v>15052</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>FISCHERWERKE GMBH &amp; CO. KG,  KLAUS-FISCHER-STR. 1,  D  72178  WALDACHTAL TUMLINGEN</t>
+        </is>
+      </c>
+      <c r="R15" t="n">
+        <v>3</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>keine aktive SDG in 2024</t>
+        </is>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>&gt;&gt; EXPORT PORTUGAL = KD.-NR. 25052 ERFASSEN !</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>150523P</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>EDI</t>
+        </is>
+      </c>
+      <c r="M16" t="n">
+        <v>805925.4100000019</v>
+      </c>
+      <c r="N16" t="n">
+        <v>15052</v>
+      </c>
+      <c r="O16" t="n">
+        <v>15052</v>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>FISCHERWERKE GMBH &amp; CO. KG,  KLAUS-FISCHER-STR. 1,  D  72178  WALDACHTAL TUMLINGEN</t>
+        </is>
+      </c>
+      <c r="R16" t="n">
+        <v>3</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>keine aktive SDG in 2024</t>
+        </is>
+      </c>
+      <c r="U16" t="n">
+        <v>5</v>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>PORTUGAL SENDUNGEN ABRECHNEN, FISCHER BEGUT- | SCHRIFTET DIE NICHT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>350523GB</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2 - wird benötigt in der Abrechnung - betrifft aber auch Erfassung</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Manuelle Erfassung</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
+        <v>41923.27999999997</v>
+      </c>
+      <c r="N17" t="n">
+        <v>35052</v>
+      </c>
+      <c r="O17" t="n">
+        <v>35052</v>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>FISCHERWERKE GMBH &amp; CO. KG,  KLAUS-FISCHER-STR. 1,  D  72178  WALDACHTAL TUMLINGEN</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>350523GB</t>
+        </is>
+      </c>
+      <c r="R17" t="n">
+        <v>3</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>doppelt</t>
+        </is>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>&gt; Bei allen Postcodes A U S S E R   OX |   bitte je Stellplatz 600 kg frachtpflichtiges |   Gewicht erfassen !!! | &gt; AB SOFORT ABLIEFERBELEG PER MAIL MIT BEZUG AUF |   UNSERE RG NR. AN BUCHHALTUNG@FISCHER.DE</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>250522</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2 - wird benötigt in der Abrechnung - betrifft aber auch Erfassung</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>EDI</t>
+        </is>
+      </c>
+      <c r="M18" t="n">
+        <v>118075.73</v>
+      </c>
+      <c r="N18" t="n">
+        <v>25052</v>
+      </c>
+      <c r="O18" t="n">
+        <v>25052</v>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>FISCHERWERKE GMBH &amp; CO. KG,  KLAUS-FISCHER-STR. 1,  D  72178  WALDACHTAL TUMLINGEN</t>
+        </is>
+      </c>
+      <c r="R18" t="n">
+        <v>2</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>betrifft Konditionierung</t>
+        </is>
+      </c>
+      <c r="U18" t="n">
+        <v>5</v>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>ABLIEFERBELEGE PER MAIL MIT BEZUG AUF UNSERE | RG-NUMMER AN |       INGEBORG.SCHNEIDDER@FISCHER.DE | ABLAUF: AUS RETRIEVEL SENDEN | ODER VON HOMEPAGE ZWISCHENSPEICHERN UND SENDEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>250522E</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>EDI</t>
+        </is>
+      </c>
+      <c r="M19" t="n">
+        <v>118075.73</v>
+      </c>
+      <c r="N19" t="n">
+        <v>25052</v>
+      </c>
+      <c r="O19" t="n">
+        <v>25052</v>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>FISCHERWERKE GMBH &amp; CO. KG,  KLAUS-FISCHER-STR. 1,  D  72178  WALDACHTAL TUMLINGEN</t>
+        </is>
+      </c>
+      <c r="R19" t="n">
+        <v>2</v>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>keine aktive SDG in 2024</t>
+        </is>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>KLEINSENDUNGEN BIS 50 KG AUS MONTROIG -&gt; BITTE | 0,1 STELLPLÄTZE ALS SPERRIGKEIT ERFASSEN | ************************************************** | 60 X 40 BIS MAX 100 KG = HALBPALETTE ERFASSEN | ************************************************** | ANSONSTEN ANZAHL DER STELLPLÄTZE ERFASSEN | (0,4 LM = 1 STELLPLATZ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>250522E</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>EDI</t>
+        </is>
+      </c>
+      <c r="M20" t="n">
+        <v>118075.73</v>
+      </c>
+      <c r="N20" t="n">
+        <v>25052</v>
+      </c>
+      <c r="O20" t="n">
+        <v>25052</v>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>FISCHERWERKE GMBH &amp; CO. KG,  KLAUS-FISCHER-STR. 1,  D  72178  WALDACHTAL TUMLINGEN</t>
+        </is>
+      </c>
+      <c r="R20" t="n">
+        <v>2</v>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>keine aktive SDG in 2024</t>
+        </is>
+      </c>
+      <c r="U20" t="n">
+        <v>5</v>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>BEI KARTONWARE BIS 50 KG € 51,-- LT.HR.BAUER | AB E-43300 MONTROIG BIS 50 KG /0,3 CBM € 39,50 | 2. LADESTELLE SCHUON?? -&gt; BEHANDLUNGSHINWEIS 43 !! | AB 18.11.13 EX E-433 MONTROIG | PAKETE BIS 50 KG -&gt; 39,50 | HALBPALETTEN BIS MAX 100 KG -&gt; 65 € | DARÜBER WIE GEHABT AUF STELLPLATZBASIS</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>250522I</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>EDI</t>
+        </is>
+      </c>
+      <c r="M21" t="n">
+        <v>118075.73</v>
+      </c>
+      <c r="N21" t="n">
+        <v>25052</v>
+      </c>
+      <c r="O21" t="n">
+        <v>25052</v>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>FISCHERWERKE GMBH &amp; CO. KG,  KLAUS-FISCHER-STR. 1,  D  72178  WALDACHTAL TUMLINGEN</t>
+        </is>
+      </c>
+      <c r="R21" t="n">
+        <v>2</v>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>keine aktive SDG in 2024</t>
+        </is>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>--&gt; EX FISCHER PADOVA - VERSCH. ENTLADESTELLEN, |     PRO STOP EINEN AUFTRAG NACHERFASSEN. | --&gt; FZ- FISCHER PADOVA - FRANKATUR 89 + FZ 10576 | --&gt; FZ- FISCHER WALDA. - FRANKATUR 90 + FZ 15052 | --&gt; IN KSP BITTE LM + STPL EINTRAGEN | --&gt; VD-SSP - BITTE NUR IN DER DFÜ-SDG. EX CESPED |     DAS GESAMTVOLUMEN EINTRAGEN, NACHDEM CESPED |     UNS BERECHNEN DARF (LM ODER CBM) | --&gt; ABS. NICHT FISCHER PADOVA - FRANKATUR DER    DFÜ ÜBERNEHMEN.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>250522I</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>EDI</t>
+        </is>
+      </c>
+      <c r="M22" t="n">
+        <v>118075.73</v>
+      </c>
+      <c r="N22" t="n">
+        <v>25052</v>
+      </c>
+      <c r="O22" t="n">
+        <v>25052</v>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>FISCHERWERKE GMBH &amp; CO. KG,  KLAUS-FISCHER-STR. 1,  D  72178  WALDACHTAL TUMLINGEN</t>
+        </is>
+      </c>
+      <c r="R22" t="n">
+        <v>2</v>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>keine aktive SDG in 2024</t>
+        </is>
+      </c>
+      <c r="U22" t="n">
+        <v>5</v>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>FZ PRÜFEN -&gt; MEIST FISCHER PADOVA 10576 | WENN ABR. NACH WALD. / GESAMTVOLUMEN DES LKW ALS | BASIS ZUGRUNDE LEGEN (Z.B. ALLE SDG. EX FISCHER | PADOVA = 8 LM, DAVON 2 LM UNFREI), DANN 2 LM | BERECHNEN ZUM FRACHTSATZ VON 8 LM | --&gt; BEI GRUNDLAGE 13,6 LM FRACHTSATZ 7,70 VERW. |     (NEUE TARIFE 2018) | FAKTURIERUNG AUF EINZELRECHNUNG ÄNDERN+ RECHNUNGSTEXT</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>250523B</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>4 - betrifft Erfassung/ Abfertigung/ Operative</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>EDI</t>
+        </is>
+      </c>
+      <c r="M23" t="n">
+        <v>118075.73</v>
+      </c>
+      <c r="N23" t="n">
+        <v>25052</v>
+      </c>
+      <c r="O23" t="n">
+        <v>25052</v>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>FISCHERWERKE GMBH &amp; CO. KG,  KLAUS-FISCHER-STR. 1,  D  72178  WALDACHTAL TUMLINGEN</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>250523B</t>
+        </is>
+      </c>
+      <c r="R23" t="n">
+        <v>3</v>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>&gt; BITTE "FIS23" ERFASSEN !!!</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>250523B</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>4 - betrifft Erfassung/ Abfertigung/ Operative</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>EDI</t>
+        </is>
+      </c>
+      <c r="M24" t="n">
+        <v>118075.73</v>
+      </c>
+      <c r="N24" t="n">
+        <v>25052</v>
+      </c>
+      <c r="O24" t="n">
+        <v>25052</v>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>FISCHERWERKE GMBH &amp; CO. KG,  KLAUS-FISCHER-STR. 1,  D  72178  WALDACHTAL TUMLINGEN</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>250523B</t>
+        </is>
+      </c>
+      <c r="R24" t="n">
+        <v>3</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="U24" t="n">
+        <v>5</v>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>&gt; BITTE "FIS23" ERFASSEN !!!</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>250523I</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>4 - betrifft Erfassung/ Abfertigung/ Operative</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>EDI</t>
+        </is>
+      </c>
+      <c r="M25" t="n">
+        <v>118075.73</v>
+      </c>
+      <c r="N25" t="n">
+        <v>25052</v>
+      </c>
+      <c r="O25" t="n">
+        <v>25052</v>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>FISCHERWERKE GMBH &amp; CO. KG,  KLAUS-FISCHER-STR. 1,  D  72178  WALDACHTAL TUMLINGEN</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>250523I</t>
+        </is>
+      </c>
+      <c r="R25" t="n">
+        <v>3</v>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>&gt; BEI FISCHER PADOVA, K E I N PALETTENTAUSCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>250523GB</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2 - wird benötigt in der Abrechnung - betrifft aber auch Erfassung</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>EDI</t>
+        </is>
+      </c>
+      <c r="M26" t="n">
+        <v>118075.73</v>
+      </c>
+      <c r="N26" t="n">
+        <v>25052</v>
+      </c>
+      <c r="O26" t="n">
+        <v>25052</v>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>FISCHERWERKE GMBH &amp; CO. KG,  KLAUS-FISCHER-STR. 1,  D  72178  WALDACHTAL TUMLINGEN</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>250523GB</t>
+        </is>
+      </c>
+      <c r="R26" t="n">
+        <v>3</v>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>betrifft Konditionierung</t>
+        </is>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>&gt; Bei allen Postcodes A U S S E R   OX |   bitte je Stellplatz 600 kg frachtpflichtiges |   Gewicht erfassen !!! | &gt; AB SOFORT ABLIEFERBELEG PER MAIL MIT BEZUG AUF |   UNSERE RG NR. AN BUCHHALTUNG@FISCHER.DE</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>350523GR</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2 - wird benötigt in der Abrechnung - betrifft aber auch Erfassung</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Manuelle Erfassung</t>
+        </is>
+      </c>
+      <c r="M27" t="n">
+        <v>41923.27999999997</v>
+      </c>
+      <c r="N27" t="n">
+        <v>35052</v>
+      </c>
+      <c r="O27" t="n">
+        <v>35052</v>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>FISCHERWERKE GMBH &amp; CO. KG,  KLAUS-FISCHER-STR. 1,  D  72178  WALDACHTAL TUMLINGEN</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>350523GR</t>
+        </is>
+      </c>
+      <c r="R27" t="n">
+        <v>3</v>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>GR</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>betrifft Konditionierung</t>
+        </is>
+      </c>
+      <c r="U27" t="n">
+        <v>5</v>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>&gt; SENDUNGEN NACH GR10-19 = STELLPLÄTZE ERFASSSEN ! | &gt; SENDUNGEN REST PLZ GR  = MIN. 250KG/STELLPLATZ |                            BZW. EFFEKTIVGEWICHT !! |   AB 5 STELLPLÄTZE 500KG/STELLPLATZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>150523GB</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2 - wird benötigt in der Abrechnung - betrifft aber auch Erfassung</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>EDI</t>
+        </is>
+      </c>
+      <c r="M28" t="n">
+        <v>805925.4100000019</v>
+      </c>
+      <c r="N28" t="n">
+        <v>15052</v>
+      </c>
+      <c r="O28" t="n">
+        <v>15052</v>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>FISCHERWERKE GMBH &amp; CO. KG,  KLAUS-FISCHER-STR. 1,  D  72178  WALDACHTAL TUMLINGEN</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>150523GB</t>
+        </is>
+      </c>
+      <c r="R28" t="n">
+        <v>3</v>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>betrifft Konditionierung</t>
+        </is>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>&gt; Bei allen Postcodes A U S S E R   OX |   bitte je Stellplatz 600 kg frachtpflichtiges |   Gewicht erfassen !!! | &gt; AB SOFORT ABLIEFERBELEG PER MAIL MIT BEZUG AUF |   UNSERE RG NR. AN BUCHHALTUNG@FISCHER.DE</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>150522E</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>3 - wird benötigt in der Abrechnung</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>EDI</t>
+        </is>
+      </c>
+      <c r="M29" t="n">
+        <v>805925.4100000019</v>
+      </c>
+      <c r="N29" t="n">
+        <v>15052</v>
+      </c>
+      <c r="O29" t="n">
+        <v>15052</v>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>FISCHERWERKE GMBH &amp; CO. KG,  KLAUS-FISCHER-STR. 1,  D  72178  WALDACHTAL TUMLINGEN</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>150522E</t>
+        </is>
+      </c>
+      <c r="R29" t="n">
+        <v>2</v>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>betrifft Konditionierung</t>
+        </is>
+      </c>
+      <c r="U29" t="n">
+        <v>5</v>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>SIND 2 SDG. AUF GLEICHEM LKW -&gt; DIE KLEINE SDG (1 | KARTON BIS 50KG) MIT 35 EURO ABRECHNEN; ANSONSTEN | NACH OFFERTE | 2. LADESTELLE SCHUON?? -&gt; BEHANDLUNGSHINWEIS 43 !!</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>250523GR</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2 - wird benötigt in der Abrechnung - betrifft aber auch Erfassung</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>EDI</t>
+        </is>
+      </c>
+      <c r="M30" t="n">
+        <v>118075.73</v>
+      </c>
+      <c r="N30" t="n">
+        <v>25052</v>
+      </c>
+      <c r="O30" t="n">
+        <v>25052</v>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>FISCHERWERKE GMBH &amp; CO. KG,  KLAUS-FISCHER-STR. 1,  D  72178  WALDACHTAL TUMLINGEN</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>250523GR</t>
+        </is>
+      </c>
+      <c r="R30" t="n">
+        <v>3</v>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>GR</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>betrifft Konditionierung</t>
+        </is>
+      </c>
+      <c r="U30" t="n">
+        <v>5</v>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>&gt; SENDUNGEN NACH GR10-19 = STELLPLÄTZE ERFASSSEN ! | &gt; SENDUNGEN REST PLZ GR  = BIS 5 PAL = 250KG/STLP |                            BZW. EFFEKTIVGEWICHT !! |                            AB  6 PAL = 500KG/STLP | &gt; FRACHTSATZ GGF. ERMITTELN UND HOCHRECHNEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>150522GB</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>3 - wird benötigt in der Abrechnung</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>EDI</t>
+        </is>
+      </c>
+      <c r="M31" t="n">
+        <v>805925.4100000019</v>
+      </c>
+      <c r="N31" t="n">
+        <v>15052</v>
+      </c>
+      <c r="O31" t="n">
+        <v>15052</v>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>FISCHERWERKE GMBH &amp; CO. KG,  KLAUS-FISCHER-STR. 1,  D  72178  WALDACHTAL TUMLINGEN</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>150522GB</t>
+        </is>
+      </c>
+      <c r="R31" t="n">
+        <v>2</v>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>betrifft Konditionierung</t>
+        </is>
+      </c>
+      <c r="U31" t="n">
+        <v>5</v>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>**FÜR SDG. EX FIS NACH DÜSSELD. FIS08 VERWENDEN** | FÜR SDG. NACH DÜSSELDORF/WALDACHTAL: | AUSFUHR ENGLAND BIS 3 ZOLLPOS. 55 EURO | VERZOLLUNG DÜSSELDORF 75 EURO INCL. 3 ZOLLPOS. | VERZOLLUNG WALDACHTAL 45 EURO INCL. 3 ZOLLPOS. | - | EX FSI &gt; HORB = FSI01, NACH WALDACHTAL = FSI02</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>150522GR</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>3 - wird benötigt in der Abrechnung</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>EDI</t>
+        </is>
+      </c>
+      <c r="M32" t="n">
+        <v>805925.4100000019</v>
+      </c>
+      <c r="N32" t="n">
+        <v>15052</v>
+      </c>
+      <c r="O32" t="n">
+        <v>15052</v>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>FISCHERWERKE GMBH &amp; CO. KG,  KLAUS-FISCHER-STR. 1,  D  72178  WALDACHTAL TUMLINGEN</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>150522GR</t>
+        </is>
+      </c>
+      <c r="R32" t="n">
+        <v>2</v>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>GR</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>betrifft Konditionierung</t>
+        </is>
+      </c>
+      <c r="U32" t="n">
+        <v>5</v>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>PRO STELLPLATZ 250KG | EXPORT-OFFERTE +15%</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>250523E</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2 - wird benötigt in der Abrechnung - betrifft aber auch Erfassung</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>EDI</t>
+        </is>
+      </c>
+      <c r="M33" t="n">
+        <v>118075.73</v>
+      </c>
+      <c r="N33" t="n">
+        <v>25052</v>
+      </c>
+      <c r="O33" t="n">
+        <v>25052</v>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>FISCHERWERKE GMBH &amp; CO. KG,  KLAUS-FISCHER-STR. 1,  D  72178  WALDACHTAL TUMLINGEN</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>250523E</t>
+        </is>
+      </c>
+      <c r="R33" t="n">
+        <v>3</v>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>noch aktuell? Falls ja, bitte nähere Infos.</t>
+        </is>
+      </c>
+      <c r="U33" t="n">
+        <v>5</v>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>AB 01.12.13 &gt; SENDUNGEN FÜR FISCHER, MONT ROIG |  - MINIMUM FÜR STELLPLATZ-SENDUNGEN = 8 STLP. |  - ADR KARTON SENDUNGEN WERDEN MIT DIESER SENDUNG |    ZUSAMMENGEFASST, KEINE STELLPLATZ-ABRECHNUNG |    MEHR. | SDG. BERNER SIND IMMER FISCHER DEUTSCHLAND-&gt;43217</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>250523P</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>3 - wird benötigt in der Abrechnung</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>EDI</t>
+        </is>
+      </c>
+      <c r="M34" t="n">
+        <v>118075.73</v>
+      </c>
+      <c r="N34" t="n">
+        <v>25052</v>
+      </c>
+      <c r="O34" t="n">
+        <v>25052</v>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>FISCHERWERKE GMBH &amp; CO. KG,  KLAUS-FISCHER-STR. 1,  D  72178  WALDACHTAL TUMLINGEN</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>250523P</t>
+        </is>
+      </c>
+      <c r="R34" t="n">
+        <v>3</v>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>betrifft Konditionierung</t>
+        </is>
+      </c>
+      <c r="U34" t="n">
+        <v>5</v>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>&gt; PORTUGAL SENDUNGEN ABRECHNEN, FISCHER BEGUT- |   SCHRIFTET DIE NICHT = 25052 | &gt; SENDUNGEN FÜR CASA DO FAROL, LAGOA IMMER |   EINZELBERECHNUNG AN 25052</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>350523</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2 - wird benötigt in der Abrechnung - betrifft aber auch Erfassung</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Manuelle Erfassung</t>
+        </is>
+      </c>
+      <c r="M35" t="n">
+        <v>41923.27999999997</v>
+      </c>
+      <c r="N35" t="n">
+        <v>35052</v>
+      </c>
+      <c r="O35" t="n">
+        <v>35052</v>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>FISCHERWERKE GMBH &amp; CO. KG,  KLAUS-FISCHER-STR. 1,  D  72178  WALDACHTAL TUMLINGEN</t>
+        </is>
+      </c>
+      <c r="R35" t="n">
+        <v>3</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Hinweis für Operative offen
+Abrechnungshinweis offen</t>
+        </is>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>&gt; BITTE AUF FIRMIERUNG ACHTEN. | &gt; 43217 = FISCHER DEUTSCHLAND VERTRIEBS GMBH | &gt; FIS03 = FISCHERWERKE, HORB-ALTHEIM | &gt; 11999 = FISCHER AUTOMOTIVE HORB | &gt; EXP AT + BE IT IMMER "FP" ERFASSEN. | &gt; EMPFÄNGER BERNER ? &gt; FZ = 43217 !!! | LIEFERSCHEINNUMMER  U N D  TRANSPORTNUMMER  !!!!ZWEITE LADESTELLE -&gt; BEHANDLUNGSHINWEIS 43 BITTE.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>350522E</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Manuelle Erfassung</t>
+        </is>
+      </c>
+      <c r="M36" t="n">
+        <v>41923.27999999997</v>
+      </c>
+      <c r="N36" t="n">
+        <v>35052</v>
+      </c>
+      <c r="O36" t="n">
+        <v>35052</v>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>FISCHERWERKE GMBH &amp; CO. KG,  KLAUS-FISCHER-STR. 1,  D  72178  WALDACHTAL TUMLINGEN</t>
+        </is>
+      </c>
+      <c r="R36" t="n">
+        <v>2</v>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>keine aktive SDG in 2024</t>
+        </is>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>KLEINSENDUNGEN BIS 50 KG AUS MONTROIG -&gt; BITTE | 0,1 STELLPLÄTZE ALS SPERRIGKEIT ERFASSEN | ************************************************** | 60 X 40 BIS MAX 100 KG = HALBPALETTE ERFASSEN | ************************************************** | ANSONSTEN ANZAHL DER STELLPLÄTZE ERFASSEN | (0,4 LM = 1 STELLPLATZ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>350522E</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Manuelle Erfassung</t>
+        </is>
+      </c>
+      <c r="M37" t="n">
+        <v>41923.27999999997</v>
+      </c>
+      <c r="N37" t="n">
+        <v>35052</v>
+      </c>
+      <c r="O37" t="n">
+        <v>35052</v>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>FISCHERWERKE GMBH &amp; CO. KG,  KLAUS-FISCHER-STR. 1,  D  72178  WALDACHTAL TUMLINGEN</t>
+        </is>
+      </c>
+      <c r="R37" t="n">
+        <v>2</v>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>keine aktive SDG in 2024</t>
+        </is>
+      </c>
+      <c r="U37" t="n">
+        <v>5</v>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>BEI KARTONWARE BIS 50 KG € 51,-- LT.HR.BAUER | AB E-43300 MONTROIG BIS 50 KG /0,3 CBM € 39,50 | 2. LADESTELLE SCHUON?? -&gt; BEHANDLUNGSHINWEIS 43 !! | AB 18.11.13 EX E-433 MONTROIG | PAKETE BIS 50 KG -&gt; 39,50 | HALBPALETTEN BIS MAX 100 KG -&gt; 65 € | DARÜBER WIE GEHABT AUF STELLPLATZBASIS</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>350522I</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Manuelle Erfassung</t>
+        </is>
+      </c>
+      <c r="M38" t="n">
+        <v>41923.27999999997</v>
+      </c>
+      <c r="N38" t="n">
+        <v>35052</v>
+      </c>
+      <c r="O38" t="n">
+        <v>35052</v>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>FISCHERWERKE GMBH &amp; CO. KG,  KLAUS-FISCHER-STR. 1,  D  72178  WALDACHTAL TUMLINGEN</t>
+        </is>
+      </c>
+      <c r="R38" t="n">
+        <v>2</v>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>keine aktive SDG in 2024</t>
+        </is>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>--&gt; EX FISCHER PADOVA - VERSCH. ENTLADESTELLEN, |     PRO STOP EINEN AUFTRAG NACHERFASSEN. | --&gt; FZ- FISCHER PADOVA - FRANKATUR 89 + FZ 10576 | --&gt; FZ- FISCHER WALDA. - FRANKATUR 90 + FZ 15052 | --&gt; IN KSP BITTE LM + STPL EINTRAGEN | --&gt; VD-SSP - BITTE NUR IN DER DFÜ-SDG. EX CESPED |     DAS GESAMTVOLUMEN EINTRAGEN, NACHDEM CESPED |     UNS BERECHNEN DARF (LM ODER CBM) | --&gt; ABS. NICHT FISCHER PADOVA - FRANKATUR DER    DFÜ ÜBERNEHMEN.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>350522I</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Manuelle Erfassung</t>
+        </is>
+      </c>
+      <c r="M39" t="n">
+        <v>41923.27999999997</v>
+      </c>
+      <c r="N39" t="n">
+        <v>35052</v>
+      </c>
+      <c r="O39" t="n">
+        <v>35052</v>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>FISCHERWERKE GMBH &amp; CO. KG,  KLAUS-FISCHER-STR. 1,  D  72178  WALDACHTAL TUMLINGEN</t>
+        </is>
+      </c>
+      <c r="R39" t="n">
+        <v>2</v>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>keine aktive SDG in 2024</t>
+        </is>
+      </c>
+      <c r="U39" t="n">
+        <v>5</v>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>FZ PRÜFEN -&gt; MEIST FISCHER PADOVA 10576 | WENN ABR. NACH WALD. / GESAMTVOLUMEN DES LKW ALS | BASIS ZUGRUNDE LEGEN (Z.B. ALLE SDG. EX FISCHER | PADOVA = 8 LM, DAVON 2 LM UNFREI), DANN 2 LM | BERECHNEN ZUM FRACHTSATZ VON 8 LM | --&gt; BEI GRUNDLAGE 13,6 LM FRACHTSATZ 7,70 VERW. |     (NEUE TARIFE 2018) | FAKTURIERUNG AUF EINZELRECHNUNG ÄNDERN+ RECHNUNGSTEXT</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>350523B</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Manuelle Erfassung</t>
+        </is>
+      </c>
+      <c r="M40" t="n">
+        <v>41923.27999999997</v>
+      </c>
+      <c r="N40" t="n">
+        <v>35052</v>
+      </c>
+      <c r="O40" t="n">
+        <v>35052</v>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>FISCHERWERKE GMBH &amp; CO. KG,  KLAUS-FISCHER-STR. 1,  D  72178  WALDACHTAL TUMLINGEN</t>
+        </is>
+      </c>
+      <c r="R40" t="n">
+        <v>3</v>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>keine aktive SDG in 2024</t>
+        </is>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>&gt; BITTE "FIS23" ERFASSEN !!!</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>350523B</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Manuelle Erfassung</t>
+        </is>
+      </c>
+      <c r="M41" t="n">
+        <v>41923.27999999997</v>
+      </c>
+      <c r="N41" t="n">
+        <v>35052</v>
+      </c>
+      <c r="O41" t="n">
+        <v>35052</v>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>FISCHERWERKE GMBH &amp; CO. KG,  KLAUS-FISCHER-STR. 1,  D  72178  WALDACHTAL TUMLINGEN</t>
+        </is>
+      </c>
+      <c r="R41" t="n">
+        <v>3</v>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>keine aktive SDG in 2024</t>
+        </is>
+      </c>
+      <c r="U41" t="n">
+        <v>5</v>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>&gt; BITTE "FIS23" ERFASSEN !!!</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>350523I</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>4 - betrifft Erfassung/ Abfertigung/ Operative</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Manuelle Erfassung</t>
+        </is>
+      </c>
+      <c r="M42" t="n">
+        <v>41923.27999999997</v>
+      </c>
+      <c r="N42" t="n">
+        <v>35052</v>
+      </c>
+      <c r="O42" t="n">
+        <v>35052</v>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>FISCHERWERKE GMBH &amp; CO. KG,  KLAUS-FISCHER-STR. 1,  D  72178  WALDACHTAL TUMLINGEN</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>350523I</t>
+        </is>
+      </c>
+      <c r="R42" t="n">
+        <v>3</v>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>&gt; BEI FISCHER PADOVA, K E I N PALETTENTAUSCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>350523P</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Manuelle Erfassung</t>
+        </is>
+      </c>
+      <c r="M43" t="n">
+        <v>41923.27999999997</v>
+      </c>
+      <c r="N43" t="n">
+        <v>35052</v>
+      </c>
+      <c r="O43" t="n">
+        <v>35052</v>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>FISCHERWERKE GMBH &amp; CO. KG,  KLAUS-FISCHER-STR. 1,  D  72178  WALDACHTAL TUMLINGEN</t>
+        </is>
+      </c>
+      <c r="R43" t="n">
+        <v>3</v>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>keine aktive SDG in 2024</t>
+        </is>
+      </c>
+      <c r="U43" t="n">
+        <v>5</v>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>PORTUGAL SENDUNGEN ABRECHNEN, FISCHER BEGUT- | SCHRIFTET DIE NICHT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>250523DK</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2 - wird benötigt in der Abrechnung - betrifft aber auch Erfassung</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>EDI</t>
+        </is>
+      </c>
+      <c r="M44" t="n">
+        <v>118075.73</v>
+      </c>
+      <c r="N44" t="n">
+        <v>25052</v>
+      </c>
+      <c r="O44" t="n">
+        <v>25052</v>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>FISCHERWERKE GMBH &amp; CO. KG,  KLAUS-FISCHER-STR. 1,  D  72178  WALDACHTAL TUMLINGEN</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>250523DK</t>
+        </is>
+      </c>
+      <c r="R44" t="n">
+        <v>3</v>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>betrifft Konditionierung</t>
+        </is>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>BITTE IN DER SPEDISPERRIGKEIT EBENFALLS STELL- | PLÄTZE ERFASSEN, WIR HABEN HIER TARIFE MIT DEM | PARTNER AUF DIESER BASIS !!!!!</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>250523</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>4 - betrifft Erfassung/ Abfertigung/ Operative</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Kobes</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Leergut</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>EDI</t>
+        </is>
+      </c>
+      <c r="M45" t="n">
+        <v>118075.73</v>
+      </c>
+      <c r="N45" t="n">
+        <v>25052</v>
+      </c>
+      <c r="O45" t="n">
+        <v>25052</v>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>FISCHERWERKE GMBH &amp; CO. KG,  KLAUS-FISCHER-STR. 1,  D  72178  WALDACHTAL TUMLINGEN</t>
+        </is>
+      </c>
+      <c r="R45" t="n">
+        <v>3</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>&gt; BITTE AUF FIRMIERUNG ACHTEN. | &gt; 43217 = FISCHER DEUTSCHLAND VERTRIEBS GMBH | &gt; FIS03 = FISCHERWERKE, HORB-ALTHEIM | &gt; 11999 = FISCHER AUTOMOTIVE HORB | &gt; EXP AT + BE IT IMMER "FP" ERFASSEN. | &gt; EMPFÄNGER BERNER ? &gt; FZ = 43217 !!! | LIEFERSCHEINNUMMER  U N D  TRANSPORTNUMMER  !!!!ZWEITE LADESTELLE -&gt; BEHANDLUNGSHINWEIS 43 BITTE.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>350523E</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2 - wird benötigt in der Abrechnung - betrifft aber auch Erfassung</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Manuelle Erfassung</t>
+        </is>
+      </c>
+      <c r="M46" t="n">
+        <v>41923.27999999997</v>
+      </c>
+      <c r="N46" t="n">
+        <v>35052</v>
+      </c>
+      <c r="O46" t="n">
+        <v>35052</v>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>FISCHERWERKE GMBH &amp; CO. KG,  KLAUS-FISCHER-STR. 1,  D  72178  WALDACHTAL TUMLINGEN</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>350523E</t>
+        </is>
+      </c>
+      <c r="R46" t="n">
+        <v>3</v>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>noch aktuell? Falls ja, bitte nähere Infos.</t>
+        </is>
+      </c>
+      <c r="U46" t="n">
+        <v>5</v>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>AB 01.12.13 &gt; SENDUNGEN FÜR FISCHER, MONT ROIG |  - MINIMUM FÜR STELLPLATZ-SENDUNGEN = 8 STLP. |  - ADR KARTON SENDUNGEN WERDEN MIT DIESER SENDUNG |    ZUSAMMENGEFASST, KEINE STELLPLATZ-ABRECHNUNG |    MEHR. | SDG. BERNER SIND IMMER FISCHER DEUTSCHLAND-&gt;43217</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>150522GB</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>3 - wird benötigt in der Abrechnung</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>EDI</t>
+        </is>
+      </c>
+      <c r="M47" t="n">
+        <v>805925.4100000019</v>
+      </c>
+      <c r="N47" t="n">
+        <v>15052</v>
+      </c>
+      <c r="O47" t="n">
+        <v>15052</v>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>FISCHERWERKE GMBH &amp; CO. KG,  KLAUS-FISCHER-STR. 1,  D  72178  WALDACHTAL TUMLINGEN</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>150522GB</t>
+        </is>
+      </c>
+      <c r="R47" t="n">
+        <v>2</v>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>betrifft Zoll-/EUST-Abrechnung</t>
+        </is>
+      </c>
+      <c r="U47" t="n">
+        <v>6</v>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>EUST-BERECHNUNG AN FISCHER MIT STEUERBESCHEID | AUSSCHL. PER MAIL SENDEN. | VORLAGE IST INNERHALB 10 TAGEN ABZUGSFÄHIG | (BEI UNIFAKT KANN DER TEXTSCHLÜSSEL ABGEÄNDERT WER | DEN) | invoices@fischer.de +  Nadine.Dubiel@fischer.de |  +  customs@fischer.de</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/output/cluster_vergleich/409480_Fischerwerke_GmbH___Co__KG_cluster.xlsx
+++ b/output/cluster_vergleich/409480_Fischerwerke_GmbH___Co__KG_cluster.xlsx
@@ -793,10 +793,10 @@
         <v>516.88</v>
       </c>
       <c r="W4" s="6" t="n">
-        <v>-13.51999999999998</v>
+        <v>-62.60169999999999</v>
       </c>
       <c r="X4" s="6" t="n">
-        <v>-2.549019607843134</v>
+        <v>-11.80273378582202</v>
       </c>
       <c r="Y4" s="5" t="inlineStr">
         <is>
